--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +51,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,2144 +439,2154 @@
   </sheetPr>
   <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Input length type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Expected output</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Actual output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Singlish input types covered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Evidence or rationale for the input type covered</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Neg_0001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>oya meka kalada nedda?</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>ඔයා මේක කළාද නැද්ද?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>ඕයා මේක කළාද නැද්ද.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Question forms</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Rationale: The sentence is a question</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Neg_0002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>ai oya hemadama mehema parakku wela enne kiyala kiyanna puluwanda?</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>ඇයි ඔයා හැමදාම මෙහෙම පරක්කු වෙලා එන්නේ කියලා කියන්න පුළුවන්ද?</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>ඇයි ඕයා හැමදාම මෙහෙම පරකකු වෙලා එන්නේ කියලා කියන්න පුළුවන්ද.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Question forms</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Rationale: The message asks a direct question</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Neg_0003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>gihin eka aran enna!</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ගිහින් ඒක අරන් එන්න!</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>ගිහින් එක අරන් එන්න!</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Command forms</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Rationale: Gives a direct command to someone</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Neg_0004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>me pituwa kiyawala iwara wela mata call ekak ganna.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>මේ පිටුව කියවලා ඉවර වෙලා මට කෝල් එකක් ගන්න.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>මේ පිටුව කියවලා ඉවර වෙලා මට කෝල් එකක ගන්න.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Command forms</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Rationale: Gives an instruction/command</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Neg_0005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>subha udesanak wewa okkotama, ada dawasa hoda wenna kiyala prarthana karanawa.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>සුභ උදෑසනක් වේවා ඔක්කොටම, අද දවස හොඳ වෙන්න කියලා ප්‍රාර්ථනා කරනවා.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>සුභ උදෑසනක වේවා ඕකකොටම, අද දවස හොඳ වෙන්න කියලා ප්‍රාර්ථනා කරනවා.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Greetings</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the greeting subha udesanak</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Neg_0006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>subha rathriyak yaluwe!</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>සුභ රාත්‍රියක් යාළුවේ!</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>සුභ රාත්‍රියක යාළුවේ!</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Greetings</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the greeting subha rathriyak</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Neg_0007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>ane poddak meka allagannako.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>අනේ පොඩ්ඩක් මේක අල්ලගන්නකෝ.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>අනේ පොඩ්ඩක මේක අල්ලගන්නකෝ.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Rationale: Makes a polite request</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Neg_0008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>karunakarala mage wahanaya me thanin ainkaranna idadenna puluwanda?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>කරුණාකරලා මගේ වාහනය මේ තැනින් අයින්කරන්න ඉඩදෙන්න පුළුවන්ද?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>කරුණාකරලා මගේ වාහනය මේ තැනින් අයින්කරන්න ඉඩදෙන්න පුළුවන්ද.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Rationale: Makes a polite request using karunakarala</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Neg_0009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>ow, mama eka dekka.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>ඔව්, මම ඒක දැක්කා.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>ඕව්, මම එක දැකකා.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Responses</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Rationale: Responds with an agreement (ow)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Neg_0010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>ne ne, eka ehema nemei wenne, mama wisthara karannam.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>නෑ නෑ, ඒක එහෙම නෙමෙයි වෙන්නේ, මම විස්තර කරන්නම්.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>නෑ නෑ, එක එහෙම නෙමෙයි වෙන්නේ, මම විස්තර කරන්නම්.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Responses</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Rationale: Responds with a disagreement (ne ne)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Neg_0011</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>hemin hemin yamu, hadissi wela wahaneta anathurak karaganna epa.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>හෙමින් හෙමින් යමු, හදිස්සි වෙලා වාහනේට අනතුරක් කරගන්න එපා.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>හෙමින් හෙමින් යමු, හදිස්සි වෙලා වාහනේට අනතුරක කරගන්න එපා.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Repeated Words</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses the repeated word 'hemin hemin'</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Neg_0012</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>ikman ikmanata enna!</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>ඉක්මන් ඉක්මනට එන්න!</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>ඉකමන් ඉකමනට එන්න!</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Repeated Words</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses the repeated word 'ikman ikmanata'</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Neg_0013</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>mokak!? oya kohomada?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>මොකක්!? ඔයා කොහොමද?</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>මොකක!. ඕයා කොහොමද.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Inputs with Punctuation Marks</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses multiple punctuation marks !?</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Neg_0014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>ow... mama hithanne eka hari... eth, sure na!</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>ඔව්... මම හිතන්නේ ඒක හරි... ඒත්, ෂුවර් නෑ!</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>ඕව්... මම හිතන්නේ එක හරි... එත්, ෂුවර් නෑ!</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Inputs with Punctuation Marks</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses ellipses and exclamation marks</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Neg_0015</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>mn oyt kiwe ehma krnna epa kyla, eth oya ahuwe na ne.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>මං ඔයාට කිව්වේ එහෙම කරන්න එපා කියලා, ඒත් ඔයා ඇහුවේ නෑ නේ.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>මං ඕයාට කිව්වේ එහෙම කරන්න එපා කියලා, එත් ඕයා ඇහුවේ නෑ නේ.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Romanization / Spelling Variants</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses shortened words like 'mn', 'oyt', 'krnna'</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Neg_0016</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>khmda itn vistar?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>කොහොමද ඉතින් විස්තර?</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>කොහොමද ඉතින් විස්තර.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Romanization / Spelling Variants</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses shortened words like 'khmda', 'itn'</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Neg_0017</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>api heta class eka iwara wela tution ekata yamuda?</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>අපි හෙට ක්ලාස් එක ඉවර වෙලා ටියුෂන් එකට යමුද?</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>අපි හෙට කලාස් එක ඉවර වෙලා ටියුෂන් එකට යමුද.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Isolated English Word Insertions</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Rationale: Inserts isolated English words 'class', 'tution'</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Neg_0018</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>mata ticket ekak ganna one.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>මට ටිකට් එකක් ගන්න ඕනේ.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>මට ටිකට් එකක ගන්න ඕනේ.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Isolated English Word Insertions</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Rationale: Inserts isolated English word 'ticket'</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Neg_0019</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>mama den out of town inne, next week eke meet wemu.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>මම දැන් අවුට් ඔෆ් ටවුන් ඉන්නේ, නෙක්ස්ට් වීක් එකේ මීට් වෙමු.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>මම දැන් අවුට් ඕෆ් ටවුන් ඉන්නේ, නෙකස්ට් වීක එකේ මීට් වෙමු.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Multi-Word English Phrases</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses phrases like 'out of town', 'next week'</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Neg_0020</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>eka mara case eka neda, we need to find a better solution for this issue as soon as possible nathnam prashne thawath wadi wenawa, so let's discuss this matter in the evening meeting after everyone arrives to the office kiyala thamai mama hithanne, mokada me wage prashna kal danna hoda na, ikmanata wisadaganna one, ethakota anith ayata weda karagena yanna lesi wenawa.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>ඒක මාර කේස් එක නේද, වී නීඩ් ටු ෆයින්ඩ් අ බෙටර් සොලියුෂන් ෆෝ දිස් ඉෂූ ඈස් සූන් ඈස් පොසිබල් නැත්නම් ප්‍රශ්නේ තවත් වැඩි වෙනවා, සෝ ලෙට්ස් ඩිස්කස් දිස් මැටර් ඉන් ද ඊවිනින් මීටිං ආෆ්ටර් එව්රිවන් අරයිව්ස් ටු ද ඔෆිස් කියලා තමයි මම හිතන්නේ, මොකද මේ වගේ ප්‍රශ්න කල් දාන්න හොඳ නෑ, ඉක්මනට විසඳගන්න ඕනේ, එතකොට අනිත් අයට වැඩ කරගෙන යන්න ලේසි වෙනවා.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>එක මාර කේස් එක නේද, වී නීඩ් ටු ෆයින්ඩ් අ බෙටර් සොලියුෂන් ෆෝ දිස් ඉෂූ ඈස් සූන් ඈස් පොසිබල් නැත්නම් ප්‍රශ්නේ තවත් වැඩි වෙනවා, සෝ ලෙට්ස් ඩිස්කස් දිස් මැටර් ඉන් ද ඊවිනින් මීටිං ආෆ්ටර් එව්රිවන් අරයිව්ස් ටු ද ඕෆිස් කියලා තමයි මම හිතන්නේ, මොකද මේ වගේ ප්‍රශ්න කල් දාන්න හොඳ නෑ, ඉකමනට විසඳගන්න ඕනේ, එතකොට අනිත් අයට වැඩ කරගෙන යන්න ලේසි වෙනවා.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Multi-Word English Phrases</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes long English phrases in the middle of Singlish</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Neg_0021</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>mage router eka wada na.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>මගේ රවුටර් එක වැඩ නෑ.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>මගේ රවුටර් එක වැඩ නෑ.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>English Digital Terms</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses digital term 'router'</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Neg_0022</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>oya software eka download karala install karanna puluwanda?</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>ඔයා සොෆ්ට්වෙයාර් එක ඩවුන්ලෝඩ් කරලා ඉන්ස්ටෝල් කරන්න පුළුවන්ද?</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>ඕයා සොෆ්ට්වෙයාර් එක ඩවුන්ලෝඩ් කරලා ඉන්ස්ටෝල් කරන්න පුළුවන්ද.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>English Digital Terms</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses digital terms like 'software', 'download', 'install'</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Neg_0023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>mama eka Facebook eke dekka.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>මම ඒක ෆේස්බුක් එකේ දැක්කා.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>මම එක ෆේස්බුක එකේ දැකකා.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Platform/App Names</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the platform name 'Facebook'</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Neg_0024</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>YouTube eke thiyena video eka balala Instagram eken share karanna.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>යූටියුබ් එකේ තියෙන වීඩියෝ එක බලලා ඉන්ස්ටග්‍රෑම් එකෙන් ශෙයා කරන්න.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>යූටියුබ් එකේ තියෙන වීඩියෝ එක බලලා ඉන්ස්ටග්‍රෑම් එකෙන් ශෙයා කරන්න.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Platform/App Names</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes platform names 'YouTube', 'Instagram'</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Neg_0025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>CEO gen approval eka ganna.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>සීඊඕ ගෙන් අපෘවල් එක ගන්න.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>සීඊඕ ගෙන් අපෘවල් එක ගන්න.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>English Abbreviations</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses the abbreviation 'CEO'</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Neg_0026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>eka VIP kenekta witharai allowed kiyala HR eken kiwwa.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>ඒක වීඅයිපී කෙනෙක්ට විතරයි අලව්ඩ් කියලා එච්ආර් එකෙන් කිව්වා.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>එක වීඅයිපී කෙනෙකට විතරයි අලව්ඩ් කියලා එච්ආර් එකෙන් කිව්වා.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>English Abbreviations</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses the abbreviations 'VIP', 'HR'</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Neg_0027</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>api lab ekata yamu.</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>අපි ලැබ් එකට යමු.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>අපි ලැබ් එකට යමු.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>English Clipped Forms</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses clipped form 'lab' (laboratory)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Neg_0028</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>heta exam eka thiyenawa, e nisa math ekka gym enna welawe na.</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>හෙට එක්සෑම් එක තියෙනවා, ඒ නිසා මාත් එක්ක ජිම් එන්න වෙලාවක් නෑ.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>හෙට එකසෑම් එක තියෙනවා, එ නිසා මාත් එකක ජිම් එන්න වෙලාවක නෑ.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>English Clipped Forms</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses clipped forms 'exam' and 'gym'</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Neg_0029</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>api Nuwara Eliye yamuda?</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>අපි නුවර එළියේ යමුද?</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>අපි නුවර එළියේ යමුද.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Place Names</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Rationale: Mentions the place 'Nuwara Eliye'</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Neg_0030</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>heta mama Colombo gihin Kandy walata yanna inne.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>හෙට මම කොළඹ ගිහින් නුවරට යන්න ඉන්නේ.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>හෙට මම කොළඹ ගිහින් නුවරට යන්න ඉන්නේ.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Place Names</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Rationale: Mentions the places 'Colombo' and 'Kandy'</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Neg_0031</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>oya Kamal wa dakkada?</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>ඔයා කමල් ව දැක්කාද?</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>ඕයා කමල් ව දැකකාද.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Person Names</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Rationale: Mentions the person name 'Kamal'</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Neg_0032</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>ada udema Nimal saha Sunil ekka katha kala.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>අද උදේම නිමල් සහ සුනිල් එක්ක කතා කළා.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>අද උදේම නිමල් සහ සුනිල් එකක කතා කළා.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Person Names</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Rationale: Mentions the person names 'Nimal' and 'Sunil'</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Neg_0033</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>salli 500k thiyenawa.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>සල්ලි 500ක් තියෙනවා.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>සල්ලි 500ක තියෙනවා.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Inputs with Numbers</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the number 500</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Neg_0034</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>lamayi 25k withara class ekata awith hitiya, eth 5k witara hitiye na.</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>ළමයි 25ක් විතර පන්තියට ඇවිත් හිටියා, ඒත් 5ක් විතර හිටියේ නෑ.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>ළමයි 25ක විතර පන්තියට ඇවිත් හිටියා, එත් 5ක විතර හිටියේ නෑ.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Inputs with Numbers</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the numbers 25 and 5</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Neg_0035</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>eka Rs. 1500k wenawa.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>ඒක රුපියල් 1500ක් වෙනවා.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>එක රුපියල් 1500ක වෙනවා.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the currency 'Rs.'</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Neg_0036</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>dollar 50k kiyanne lankawe salli walin kochcharada kiyala balanna.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>ඩොලර් 50ක් කියන්නේ ලංකාවේ සල්ලි වලින් කොච්චරද කියලා බලන්න.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>ඩොලර් 50ක කියන්නේ ලංකාවේ සල්ලි වලින් කොච්චරද කියලා බලන්න.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the currency term 'dollar'</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Neg_0037</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>udasana 8.30 ta enna.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>උදෑසන 8.30ට එන්න.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>උදෑසන 8.30ට එන්න.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Time Formats</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the time format '8.30'</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Neg_0038</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>meeting eka 10:45 AM walata patan gannawa kiyala kiwwa.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>මීටිං එක පෙ.ව. 10:45ට පටන් ගන්නවා කියලා කිව්වා.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>මීටිං එක පෙ.ව. 10:45ට පටන් ගන්නවා කියලා කිව්වා.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Time Formats</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the time format '10:45 AM'</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Neg_0039</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2024-05-12 ta lesti wemuda?</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2024-05-12 ට ලෑස්ති වෙමුද?</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2024-05-12 ට ලෑස්ති වෙමුද.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the date format '2024-05-12'</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Neg_0040</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>mage upandinaya thiyenne November 25 weni data.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>මගේ උපන්දිනය තියෙන්නේ නොවැම්බර් 25 වෙනි දාට.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>මගේ උපන්දිනය තියෙන්නේ නොවැම්බර් 25 වෙනි දාට.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the date format 'November 25'</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Neg_0041</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>meka 5kg k withara barai.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>මේක කිලෝ 5ක් විතර බරයි.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>මේක කිලෝ 5ක විතර බරයි.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Measurements</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the measurement '5kg'</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Neg_0042</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>pare dura 15km k wenawa, e nisa payin yanna amarui.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>පාරේ දුර කිලෝමීටර් 15ක් වෙනවා, ඒ නිසා පයින් යන්න අමාරුයි.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>පාරේ දුර කිලෝමීටර් 15ක වෙනවා, එ නිසා පයින් යන්න අමාරුයි.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Measurements</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes the measurement '15km'</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Neg_0043</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>ekanam patta dial ekak.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>ඒකනම් පට්ට ඩයල් එකක්.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>එකනම් පට්ට ඩයල් එකක.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>Slang</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses slang words like 'patta' and 'dial'</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Neg_0044</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>uba nam amuthuma geymak denne me dawas wala, niyamai a!</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>උඹ නම් අමුතුම ගේමක් දෙන්නේ මේ දවස් වල, නියමයි ආ!</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>උඹ නම් අමුතුම ගේමක දෙන්නේ මේ දවස් වල, නියමයි ආ!</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Slang</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses slang like 'geymak' and casual term 'uba'</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Neg_0045</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>mage email eka test@email.com</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>මගේ ඊමේල් එක test@email.com</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>මගේ ඊමේල් එක test@email.com</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Online Identifiers</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes an email address</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Neg_0046</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>oya mage facebook page eka balanna, link eka thiyenne www.facebook.com/mypage kiyala.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>ඔයා මගේ ෆේස්බුක් පේජ් එක බලන්න, ලින්ක් එක තියෙන්නේ www.facebook.com/mypage කියලා.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>ඕයා මගේ ෆේස්බුක පේජ් එක බලන්න, ලින්ක එක තියෙන්නේ www.facebook.com/mypage කියලා.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Online Identifiers</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes a URL link</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Neg_0047</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>eka nam maru 😂</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>ඒක නම් මරු 😂</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>එක නම් මරු 😂</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>Emojis</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes an emoji</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Neg_0048</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>man ada hari sathutin inne ❤️ oya ekka katha kalata passe 🌟</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>මං අද හරි සතුටින් ඉන්නේ ❤️ ඔයා එක්ක කතා කළාට පස්සේ 🌟</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>මං අද හරි සතුටින් ඉන්නේ ❤️ ඕයා එකක කතා කළාට පස්සේ 🌟</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Emojis</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Rationale: Includes emojis within the text</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Neg_0049</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>kohomad aiyye?</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>කොහොමද අයියේ?</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>කොහොමද අයියේ.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Romanization / Spelling Variants</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Rationale: Incorrect spelling like 'kohomad'</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Neg_0050</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>ado no chance bung, eka karanna wenne na kohomat.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>අඩෝ නෝ චාන්ස් බං, ඒක කරන්න වෙන්නේ නෑ කොහොමත්.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>අඩෝ නෝ චාන්ස් බං, එක කරන්න වෙන්නේ නෑ කොහොමත්.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Slang</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Rationale: Uses slang words like 'ado' and 'bung'</t>
         </is>
